--- a/output/ValueSet-attestation-provision-type-valueset.xlsx
+++ b/output/ValueSet-attestation-provision-type-valueset.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,16 +108,13 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>=</t>
+    <t>Concept</t>
   </si>
   <si>
     <t>permit</t>
+  </si>
+  <si>
+    <t>Permit</t>
   </si>
   <si>
     <t/>
@@ -316,84 +316,86 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -403,7 +405,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -412,23 +414,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s" s="2">
         <v>33</v>
       </c>
     </row>

--- a/output/ValueSet-attestation-provision-type-valueset.xlsx
+++ b/output/ValueSet-attestation-provision-type-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-attestation-provision-type-valueset.xlsx
+++ b/output/ValueSet-attestation-provision-type-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/ValueSet-attestation-provision-type-valueset.xlsx
+++ b/output/ValueSet-attestation-provision-type-valueset.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
